--- a/erp-server/erp-server-file/src/main/resources/excel/wms/otherInstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/otherInstock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>入库单号</t>
   </si>
@@ -64,6 +64,12 @@
     <t>仓位</t>
   </si>
   <si>
+    <t>第三方单号</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>审核人(最新)</t>
   </si>
   <si>
@@ -107,6 +113,12 @@
   </si>
   <si>
     <t>{.warehouseLocation}</t>
+  </si>
+  <si>
+    <t>{.thirdCode}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
   </si>
   <si>
     <t>{.approveUserName}</t>
@@ -1089,7 +1101,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1101,13 +1113,15 @@
     <col min="7" max="7" width="12.625" customWidth="1"/>
     <col min="8" max="8" width="10.5" customWidth="1"/>
     <col min="10" max="11" width="14.625" customWidth="1"/>
-    <col min="12" max="12" width="15.125" customWidth="1"/>
-    <col min="13" max="13" width="13.75" customWidth="1"/>
-    <col min="14" max="14" width="11.75" customWidth="1"/>
-    <col min="15" max="15" width="24.75" customWidth="1"/>
+    <col min="12" max="12" width="15.875" customWidth="1"/>
+    <col min="13" max="13" width="16.25" customWidth="1"/>
+    <col min="14" max="14" width="15.125" customWidth="1"/>
+    <col min="15" max="15" width="13.75" customWidth="1"/>
+    <col min="16" max="16" width="11.75" customWidth="1"/>
+    <col min="17" max="17" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1153,52 +1167,64 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/otherInstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/otherInstock.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>入库单号</t>
   </si>
@@ -67,6 +67,9 @@
     <t>第三方单号</t>
   </si>
   <si>
+    <t>退货物流单号</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -116,6 +119,9 @@
   </si>
   <si>
     <t>{.thirdCode}</t>
+  </si>
+  <si>
+    <t>{.returnLogisticCode}</t>
   </si>
   <si>
     <t>{.remark}</t>
@@ -143,9 +149,23 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
-    <font>
-      <sz val="11"/>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -490,12 +510,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -616,142 +651,148 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1101,7 +1142,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1114,15 +1155,16 @@
     <col min="8" max="8" width="10.5" customWidth="1"/>
     <col min="10" max="11" width="14.625" customWidth="1"/>
     <col min="12" max="12" width="15.875" customWidth="1"/>
-    <col min="13" max="13" width="16.25" customWidth="1"/>
-    <col min="14" max="14" width="15.125" customWidth="1"/>
-    <col min="15" max="15" width="13.75" customWidth="1"/>
-    <col min="16" max="16" width="11.75" customWidth="1"/>
-    <col min="17" max="17" width="24.75" customWidth="1"/>
+    <col min="13" max="13" width="14.25" style="1" customWidth="1"/>
+    <col min="14" max="14" width="16.25" customWidth="1"/>
+    <col min="15" max="15" width="15.125" customWidth="1"/>
+    <col min="16" max="16" width="13.75" customWidth="1"/>
+    <col min="17" max="17" width="11.75" customWidth="1"/>
+    <col min="18" max="18" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:18">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -1158,7 +1200,7 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="N1" t="s">
@@ -1173,58 +1215,64 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" t="s">
         <v>29</v>
       </c>
+      <c r="M2" s="3" t="s">
+        <v>30</v>
+      </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/otherInstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/otherInstock.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>入库单号</t>
   </si>
@@ -52,6 +52,9 @@
     <t>入库日期</t>
   </si>
   <si>
+    <t>入库类型</t>
+  </si>
+  <si>
     <t>实发数量</t>
   </si>
   <si>
@@ -104,6 +107,9 @@
   </si>
   <si>
     <t>{.billDate}</t>
+  </si>
+  <si>
+    <t>{.typeName}</t>
   </si>
   <si>
     <t>{.actualQty}</t>
@@ -1142,7 +1148,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -1152,18 +1158,19 @@
     <col min="5" max="5" width="13.5" customWidth="1"/>
     <col min="6" max="6" width="15.75" customWidth="1"/>
     <col min="7" max="7" width="12.625" customWidth="1"/>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="10" max="11" width="14.625" customWidth="1"/>
-    <col min="12" max="12" width="15.875" customWidth="1"/>
-    <col min="13" max="13" width="14.25" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16.25" customWidth="1"/>
-    <col min="15" max="15" width="15.125" customWidth="1"/>
-    <col min="16" max="16" width="13.75" customWidth="1"/>
-    <col min="17" max="17" width="11.75" customWidth="1"/>
-    <col min="18" max="18" width="24.75" customWidth="1"/>
+    <col min="8" max="8" width="17.375" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="11" max="12" width="14.625" customWidth="1"/>
+    <col min="13" max="13" width="15.875" customWidth="1"/>
+    <col min="14" max="14" width="14.25" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.25" customWidth="1"/>
+    <col min="16" max="16" width="15.125" customWidth="1"/>
+    <col min="17" max="17" width="13.75" customWidth="1"/>
+    <col min="18" max="18" width="11.75" customWidth="1"/>
+    <col min="19" max="19" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1200,10 +1207,10 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
       <c r="O1" t="s">
@@ -1218,61 +1225,67 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N2" t="s">
+      <c r="M2" t="s">
         <v>31</v>
       </c>
+      <c r="N2" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="O2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R2" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="S2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/otherInstock.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/otherInstock.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>入库单号</t>
   </si>
@@ -43,6 +43,9 @@
     <t>作废状态</t>
   </si>
   <si>
+    <t>入库类型</t>
+  </si>
+  <si>
     <t>SKU</t>
   </si>
   <si>
@@ -52,9 +55,6 @@
     <t>入库日期</t>
   </si>
   <si>
-    <t>入库类型</t>
-  </si>
-  <si>
     <t>实发数量</t>
   </si>
   <si>
@@ -100,6 +100,9 @@
     <t>{.invalidStatusName}</t>
   </si>
   <si>
+    <t>{.typeName}</t>
+  </si>
+  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
@@ -107,9 +110,6 @@
   </si>
   <si>
     <t>{.billDate}</t>
-  </si>
-  <si>
-    <t>{.typeName}</t>
   </si>
   <si>
     <t>{.actualQty}</t>
@@ -1148,29 +1148,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
     <col min="2" max="2" width="11.5" customWidth="1"/>
     <col min="3" max="3" width="14.5" customWidth="1"/>
     <col min="4" max="4" width="10.625" customWidth="1"/>
-    <col min="5" max="5" width="13.5" customWidth="1"/>
-    <col min="6" max="6" width="15.75" customWidth="1"/>
-    <col min="7" max="7" width="12.625" customWidth="1"/>
-    <col min="8" max="8" width="17.375" customWidth="1"/>
-    <col min="9" max="9" width="10.5" customWidth="1"/>
-    <col min="11" max="12" width="14.625" customWidth="1"/>
-    <col min="13" max="13" width="15.875" customWidth="1"/>
-    <col min="14" max="14" width="14.25" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.25" customWidth="1"/>
-    <col min="16" max="16" width="15.125" customWidth="1"/>
-    <col min="17" max="17" width="13.75" customWidth="1"/>
-    <col min="18" max="18" width="11.75" customWidth="1"/>
-    <col min="19" max="19" width="24.75" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="15.75" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="9" max="9" width="17.375" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="12" max="13" width="14.625" customWidth="1"/>
+    <col min="14" max="14" width="15.875" customWidth="1"/>
+    <col min="15" max="15" width="14.25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.25" customWidth="1"/>
+    <col min="17" max="17" width="15.125" customWidth="1"/>
+    <col min="18" max="18" width="13.75" customWidth="1"/>
+    <col min="19" max="19" width="11.75" customWidth="1"/>
+    <col min="20" max="20" width="24.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1196,40 +1197,43 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1255,36 +1259,39 @@
         <v>26</v>
       </c>
       <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>29</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>30</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>31</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>33</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>34</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>35</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>36</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>37</v>
       </c>
     </row>
